--- a/app/src/main/java/tps/tp1/salida/ranking.xlsx
+++ b/app/src/main/java/tps/tp1/salida/ranking.xlsx
@@ -100,7 +100,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="3">
@@ -108,7 +108,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="4">
@@ -116,7 +116,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
